--- a/CONSULTAS_OVERFORE_20260830_v2.xlsx
+++ b/CONSULTAS_OVERFORE_20260830_v2.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>El PROPONENTE no incorpora biometría en portería en la Etapa 1: mantiene el torniquete con lectura de credencial reforzado con validación documental de habilitación en línea conforme a RT-09.01, y entiende que la exigencia de biometría facial de las Bases Técnicas Transversales aplica al recinto técnico de servidores del Cap. 6 y no a la portería general.</t>
+          <t>El PROPONENTE no incorpora biometría en portería en la Etapa 1: mantiene el torniquete con lectura de credencial reforzado con validación documental de habilitación en línea dentro del umbral de 1,5 segundos que el Cap. 15 del Caso asocia al código RT-09.01 y que, conforme a la Consulta N.º 1, corresponde al numeral 9.1 del documento transversal, y entiende que la exigencia de biometría facial de las Bases Técnicas Transversales aplica al recinto técnico de servidores del Cap. 6 y no a la portería general.</t>
         </is>
       </c>
     </row>
